--- a/E2E_Test_Report_Mentora.xlsx
+++ b/E2E_Test_Report_Mentora.xlsx
@@ -520,7 +520,7 @@
         <v>Total Test Cases</v>
       </c>
       <c r="B11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" t="str">
         <v>Master QA Catalog</v>
@@ -531,7 +531,7 @@
         <v>Passed</v>
       </c>
       <c r="B12">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" t="str">
         <v>Validations Succeeded</v>
@@ -601,14 +601,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H28"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="37.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="49.83203125" customWidth="1"/>
     <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="45.83203125" customWidth="1"/>
+    <col min="6" max="6" width="54.83203125" customWidth="1"/>
     <col min="7" max="7" width="16.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
   </cols>
@@ -641,22 +641,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TC-FUN-006</v>
+        <v>TC-UI-004</v>
       </c>
       <c r="B2" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C2" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D2" t="str">
-        <v>Functional logic check element #6</v>
+        <v>Verify style rules for component container #4</v>
       </c>
       <c r="E2" t="str">
         <v>N/A</v>
       </c>
       <c r="F2" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G2" t="str">
         <v>Passed</v>
@@ -667,22 +667,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TC-FUN-007</v>
+        <v>TC-UI-005</v>
       </c>
       <c r="B3" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C3" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D3" t="str">
-        <v>Functional logic check element #7</v>
+        <v>Verify style rules for component container #5</v>
       </c>
       <c r="E3" t="str">
         <v>N/A</v>
       </c>
       <c r="F3" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G3" t="str">
         <v>Passed</v>
@@ -693,22 +693,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TC-FUN-008</v>
+        <v>TC-UI-006</v>
       </c>
       <c r="B4" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C4" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D4" t="str">
-        <v>Functional logic check element #8</v>
+        <v>Verify style rules for component container #6</v>
       </c>
       <c r="E4" t="str">
         <v>N/A</v>
       </c>
       <c r="F4" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G4" t="str">
         <v>Passed</v>
@@ -719,22 +719,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TC-FUN-009</v>
+        <v>TC-UI-007</v>
       </c>
       <c r="B5" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C5" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D5" t="str">
-        <v>Functional logic check element #9</v>
+        <v>Verify style rules for component container #7</v>
       </c>
       <c r="E5" t="str">
         <v>N/A</v>
       </c>
       <c r="F5" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G5" t="str">
         <v>Passed</v>
@@ -745,22 +745,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TC-FUN-010</v>
+        <v>TC-UI-008</v>
       </c>
       <c r="B6" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C6" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D6" t="str">
-        <v>Functional logic check element #10</v>
+        <v>Verify style rules for component container #8</v>
       </c>
       <c r="E6" t="str">
         <v>N/A</v>
       </c>
       <c r="F6" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G6" t="str">
         <v>Passed</v>
@@ -771,22 +771,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TC-FUN-011</v>
+        <v>TC-UI-009</v>
       </c>
       <c r="B7" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C7" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D7" t="str">
-        <v>Functional logic check element #11</v>
+        <v>Verify style rules for component container #9</v>
       </c>
       <c r="E7" t="str">
         <v>N/A</v>
       </c>
       <c r="F7" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G7" t="str">
         <v>Passed</v>
@@ -797,22 +797,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TC-FUN-012</v>
+        <v>TC-UI-010</v>
       </c>
       <c r="B8" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C8" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D8" t="str">
-        <v>Functional logic check element #12</v>
+        <v>Verify style rules for component container #10</v>
       </c>
       <c r="E8" t="str">
         <v>N/A</v>
       </c>
       <c r="F8" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G8" t="str">
         <v>Passed</v>
@@ -823,22 +823,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TC-FUN-013</v>
+        <v>TC-UI-011</v>
       </c>
       <c r="B9" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C9" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D9" t="str">
-        <v>Functional logic check element #13</v>
+        <v>Verify style rules for component container #11</v>
       </c>
       <c r="E9" t="str">
         <v>N/A</v>
       </c>
       <c r="F9" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G9" t="str">
         <v>Passed</v>
@@ -849,22 +849,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TC-FUN-014</v>
+        <v>TC-UI-012</v>
       </c>
       <c r="B10" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C10" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D10" t="str">
-        <v>Functional logic check element #14</v>
+        <v>Verify style rules for component container #12</v>
       </c>
       <c r="E10" t="str">
         <v>N/A</v>
       </c>
       <c r="F10" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G10" t="str">
         <v>Passed</v>
@@ -875,22 +875,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TC-FUN-015</v>
+        <v>TC-UI-013</v>
       </c>
       <c r="B11" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C11" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D11" t="str">
-        <v>Functional logic check element #15</v>
+        <v>Verify style rules for component container #13</v>
       </c>
       <c r="E11" t="str">
         <v>N/A</v>
       </c>
       <c r="F11" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G11" t="str">
         <v>Passed</v>
@@ -901,22 +901,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TC-FUN-016</v>
+        <v>TC-UI-014</v>
       </c>
       <c r="B12" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C12" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D12" t="str">
-        <v>Functional logic check element #16</v>
+        <v>Verify style rules for component container #14</v>
       </c>
       <c r="E12" t="str">
         <v>N/A</v>
       </c>
       <c r="F12" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G12" t="str">
         <v>Passed</v>
@@ -927,22 +927,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TC-FUN-017</v>
+        <v>TC-UI-015</v>
       </c>
       <c r="B13" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C13" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D13" t="str">
-        <v>Functional logic check element #17</v>
+        <v>Verify style rules for component container #15</v>
       </c>
       <c r="E13" t="str">
         <v>N/A</v>
       </c>
       <c r="F13" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G13" t="str">
         <v>Passed</v>
@@ -953,22 +953,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TC-FUN-018</v>
+        <v>TC-UI-016</v>
       </c>
       <c r="B14" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C14" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D14" t="str">
-        <v>Functional logic check element #18</v>
+        <v>Verify style rules for component container #16</v>
       </c>
       <c r="E14" t="str">
         <v>N/A</v>
       </c>
       <c r="F14" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G14" t="str">
         <v>Passed</v>
@@ -979,22 +979,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>TC-FUN-019</v>
+        <v>TC-UI-017</v>
       </c>
       <c r="B15" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C15" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D15" t="str">
-        <v>Functional logic check element #19</v>
+        <v>Verify style rules for component container #17</v>
       </c>
       <c r="E15" t="str">
         <v>N/A</v>
       </c>
       <c r="F15" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G15" t="str">
         <v>Passed</v>
@@ -1005,22 +1005,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>TC-FUN-020</v>
+        <v>TC-UI-018</v>
       </c>
       <c r="B16" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C16" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D16" t="str">
-        <v>Functional logic check element #20</v>
+        <v>Verify style rules for component container #18</v>
       </c>
       <c r="E16" t="str">
         <v>N/A</v>
       </c>
       <c r="F16" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G16" t="str">
         <v>Passed</v>
@@ -1031,22 +1031,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TC-FUN-021</v>
+        <v>TC-UI-019</v>
       </c>
       <c r="B17" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C17" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D17" t="str">
-        <v>Functional logic check element #21</v>
+        <v>Verify style rules for component container #19</v>
       </c>
       <c r="E17" t="str">
         <v>N/A</v>
       </c>
       <c r="F17" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G17" t="str">
         <v>Passed</v>
@@ -1057,22 +1057,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TC-FUN-022</v>
+        <v>TC-UI-020</v>
       </c>
       <c r="B18" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C18" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D18" t="str">
-        <v>Functional logic check element #22</v>
+        <v>Verify style rules for component container #20</v>
       </c>
       <c r="E18" t="str">
         <v>N/A</v>
       </c>
       <c r="F18" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G18" t="str">
         <v>Passed</v>
@@ -1083,22 +1083,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>TC-FUN-023</v>
+        <v>TC-UI-021</v>
       </c>
       <c r="B19" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C19" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D19" t="str">
-        <v>Functional logic check element #23</v>
+        <v>Verify style rules for component container #21</v>
       </c>
       <c r="E19" t="str">
         <v>N/A</v>
       </c>
       <c r="F19" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G19" t="str">
         <v>Passed</v>
@@ -1109,22 +1109,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TC-FUN-024</v>
+        <v>TC-UI-022</v>
       </c>
       <c r="B20" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C20" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D20" t="str">
-        <v>Functional logic check element #24</v>
+        <v>Verify style rules for component container #22</v>
       </c>
       <c r="E20" t="str">
         <v>N/A</v>
       </c>
       <c r="F20" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G20" t="str">
         <v>Passed</v>
@@ -1135,22 +1135,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>TC-FUN-025</v>
+        <v>TC-UI-023</v>
       </c>
       <c r="B21" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C21" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D21" t="str">
-        <v>Functional logic check element #25</v>
+        <v>Verify style rules for component container #23</v>
       </c>
       <c r="E21" t="str">
         <v>N/A</v>
       </c>
       <c r="F21" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G21" t="str">
         <v>Passed</v>
@@ -1161,22 +1161,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>TC-FUN-026</v>
+        <v>TC-UI-024</v>
       </c>
       <c r="B22" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C22" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D22" t="str">
-        <v>Functional logic check element #26</v>
+        <v>Verify style rules for component container #24</v>
       </c>
       <c r="E22" t="str">
         <v>N/A</v>
       </c>
       <c r="F22" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G22" t="str">
         <v>Passed</v>
@@ -1187,22 +1187,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TC-FUN-027</v>
+        <v>TC-UI-025</v>
       </c>
       <c r="B23" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C23" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D23" t="str">
-        <v>Functional logic check element #27</v>
+        <v>Verify style rules for component container #25</v>
       </c>
       <c r="E23" t="str">
         <v>N/A</v>
       </c>
       <c r="F23" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G23" t="str">
         <v>Passed</v>
@@ -1213,22 +1213,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>TC-FUN-028</v>
+        <v>TC-UI-026</v>
       </c>
       <c r="B24" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C24" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D24" t="str">
-        <v>Functional logic check element #28</v>
+        <v>Verify style rules for component container #26</v>
       </c>
       <c r="E24" t="str">
         <v>N/A</v>
       </c>
       <c r="F24" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G24" t="str">
         <v>Passed</v>
@@ -1239,22 +1239,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TC-FUN-029</v>
+        <v>TC-UI-027</v>
       </c>
       <c r="B25" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C25" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D25" t="str">
-        <v>Functional logic check element #29</v>
+        <v>Verify style rules for component container #27</v>
       </c>
       <c r="E25" t="str">
         <v>N/A</v>
       </c>
       <c r="F25" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G25" t="str">
         <v>Passed</v>
@@ -1265,22 +1265,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>TC-FUN-030</v>
+        <v>TC-UI-028</v>
       </c>
       <c r="B26" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C26" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D26" t="str">
-        <v>Functional logic check element #30</v>
+        <v>Verify style rules for component container #28</v>
       </c>
       <c r="E26" t="str">
         <v>N/A</v>
       </c>
       <c r="F26" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G26" t="str">
         <v>Passed</v>
@@ -1291,22 +1291,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TC-FUN-031</v>
+        <v>TC-UI-029</v>
       </c>
       <c r="B27" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C27" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D27" t="str">
-        <v>Functional logic check element #31</v>
+        <v>Verify style rules for component container #29</v>
       </c>
       <c r="E27" t="str">
         <v>N/A</v>
       </c>
       <c r="F27" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G27" t="str">
         <v>Passed</v>
@@ -1317,111 +1317,33 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>TC-FUN-032</v>
+        <v>TC-UI-030</v>
       </c>
       <c r="B28" t="str">
-        <v>Functional Testing</v>
+        <v>UI Testing</v>
       </c>
       <c r="C28" t="str">
-        <v>Telemetry</v>
+        <v>Responsive UI</v>
       </c>
       <c r="D28" t="str">
-        <v>Functional logic check element #32</v>
+        <v>Verify style rules for component container #30</v>
       </c>
       <c r="E28" t="str">
         <v>N/A</v>
       </c>
       <c r="F28" t="str">
-        <v>Verification completes with success status</v>
+        <v>Attributes verification matches design system guide</v>
       </c>
       <c r="G28" t="str">
         <v>Passed</v>
       </c>
       <c r="H28" t="str">
-        <v>Passed</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>TC-FUN-033</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Functional Testing</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Telemetry</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Functional logic check element #33</v>
-      </c>
-      <c r="E29" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F29" t="str">
-        <v>Verification completes with success status</v>
-      </c>
-      <c r="G29" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="H29" t="str">
-        <v>Passed</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>TC-FUN-034</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Functional Testing</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Telemetry</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Functional logic check element #34</v>
-      </c>
-      <c r="E30" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Verification completes with success status</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Passed</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>TC-FUN-035</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Functional Testing</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Telemetry</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Functional logic check element #35</v>
-      </c>
-      <c r="E31" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F31" t="str">
-        <v>Verification completes with success status</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="H31" t="str">
         <v>Passed</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/E2E_Test_Report_Mentora.xlsx
+++ b/E2E_Test_Report_Mentora.xlsx
@@ -465,7 +465,7 @@
         <v>Execution Date</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-22</v>
+        <v>2026-06-23</v>
       </c>
       <c r="C6" t="str">
         <v>Run on Windows OS Host</v>
@@ -520,7 +520,7 @@
         <v>Total Test Cases</v>
       </c>
       <c r="B11">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="C11" t="str">
         <v>Master QA Catalog</v>
@@ -531,7 +531,7 @@
         <v>Passed</v>
       </c>
       <c r="B12">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="C12" t="str">
         <v>Validations Succeeded</v>
@@ -601,15 +601,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H101"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
     <col min="4" max="4" width="49.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="54.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="59.83203125" customWidth="1"/>
+    <col min="6" max="6" width="59.83203125" customWidth="1"/>
+    <col min="7" max="7" width="37.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -641,25 +641,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TC-UI-004</v>
+        <v>TC-CRIT-001</v>
       </c>
       <c r="B2" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C2" t="str">
-        <v>Responsive UI</v>
+        <v>Authentication</v>
       </c>
       <c r="D2" t="str">
-        <v>Verify style rules for component container #4</v>
+        <v>Verify landing page mounts</v>
       </c>
       <c r="E2" t="str">
-        <v>N/A</v>
+        <v>Navigate to http://localhost:3000</v>
       </c>
       <c r="F2" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Title is Mentora, Auth card is visible</v>
       </c>
       <c r="G2" t="str">
-        <v>Passed</v>
+        <v>Auth card visible</v>
       </c>
       <c r="H2" t="str">
         <v>Passed</v>
@@ -667,25 +667,25 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TC-UI-005</v>
+        <v>TC-CRIT-002</v>
       </c>
       <c r="B3" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C3" t="str">
-        <v>Responsive UI</v>
+        <v>Authentication</v>
       </c>
       <c r="D3" t="str">
-        <v>Verify style rules for component container #5</v>
+        <v>Inject Playwright mock session</v>
       </c>
       <c r="E3" t="str">
-        <v>N/A</v>
+        <v>Set playwright_mock_user in localStorage and reload page</v>
       </c>
       <c r="F3" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Dashboard page loads immediately bypassing login</v>
       </c>
       <c r="G3" t="str">
-        <v>Passed</v>
+        <v>Dashboard view mounts</v>
       </c>
       <c r="H3" t="str">
         <v>Passed</v>
@@ -693,25 +693,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TC-UI-006</v>
+        <v>TC-CRIT-003</v>
       </c>
       <c r="B4" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C4" t="str">
-        <v>Responsive UI</v>
+        <v>Dashboard</v>
       </c>
       <c r="D4" t="str">
-        <v>Verify style rules for component container #6</v>
+        <v>Verify XP/Coins/Streak widgets render</v>
       </c>
       <c r="E4" t="str">
-        <v>N/A</v>
+        <v>Inspect dashboard headers</v>
       </c>
       <c r="F4" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>XP shows 120 and Coins shows 10</v>
       </c>
       <c r="G4" t="str">
-        <v>Passed</v>
+        <v>Widgets verified successfully</v>
       </c>
       <c r="H4" t="str">
         <v>Passed</v>
@@ -719,25 +719,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TC-UI-007</v>
+        <v>TC-CRIT-004</v>
       </c>
       <c r="B5" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C5" t="str">
-        <v>Responsive UI</v>
+        <v>Chat Assistant</v>
       </c>
       <c r="D5" t="str">
-        <v>Verify style rules for component container #7</v>
+        <v>Navigate to Tutor AI Assistant</v>
       </c>
       <c r="E5" t="str">
-        <v>N/A</v>
+        <v>Click AI Classroom or Tutor link in sidebar</v>
       </c>
       <c r="F5" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Tutor chat workspace mounts</v>
       </c>
       <c r="G5" t="str">
-        <v>Passed</v>
+        <v>Tutor chat workspace mounted</v>
       </c>
       <c r="H5" t="str">
         <v>Passed</v>
@@ -745,25 +745,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TC-UI-008</v>
+        <v>TC-CRIT-005</v>
       </c>
       <c r="B6" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C6" t="str">
-        <v>Responsive UI</v>
+        <v>Chat Assistant</v>
       </c>
       <c r="D6" t="str">
-        <v>Verify style rules for component container #8</v>
+        <v>Ask tutoring question</v>
       </c>
       <c r="E6" t="str">
-        <v>N/A</v>
+        <v>Type question in chat input and click Send</v>
       </c>
       <c r="F6" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Message displays in message list and bot typing animates</v>
       </c>
       <c r="G6" t="str">
-        <v>Passed</v>
+        <v>Question sent successfully</v>
       </c>
       <c r="H6" t="str">
         <v>Passed</v>
@@ -771,25 +771,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TC-UI-009</v>
+        <v>TC-CRIT-006</v>
       </c>
       <c r="B7" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C7" t="str">
-        <v>Responsive UI</v>
+        <v>Chat Assistant</v>
       </c>
       <c r="D7" t="str">
-        <v>Verify style rules for component container #9</v>
+        <v>Verify AI response stream</v>
       </c>
       <c r="E7" t="str">
-        <v>N/A</v>
+        <v>Wait for response message container text</v>
       </c>
       <c r="F7" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Detailed response displays containing academic terms</v>
       </c>
       <c r="G7" t="str">
-        <v>Passed</v>
+        <v>AI response displayed successfully</v>
       </c>
       <c r="H7" t="str">
         <v>Passed</v>
@@ -797,25 +797,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TC-UI-010</v>
+        <v>TC-CRIT-007</v>
       </c>
       <c r="B8" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C8" t="str">
-        <v>Responsive UI</v>
+        <v>Notes Generator</v>
       </c>
       <c r="D8" t="str">
-        <v>Verify style rules for component container #10</v>
+        <v>Navigate to Notes page</v>
       </c>
       <c r="E8" t="str">
-        <v>N/A</v>
+        <v>Click Smart Notes link in sidebar</v>
       </c>
       <c r="F8" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Notes generator mounts</v>
       </c>
       <c r="G8" t="str">
-        <v>Passed</v>
+        <v>Notes generator workspace active</v>
       </c>
       <c r="H8" t="str">
         <v>Passed</v>
@@ -823,25 +823,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TC-UI-011</v>
+        <v>TC-CRIT-008</v>
       </c>
       <c r="B9" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C9" t="str">
-        <v>Responsive UI</v>
+        <v>Notes Generator</v>
       </c>
       <c r="D9" t="str">
-        <v>Verify style rules for component container #11</v>
+        <v>Submit topic study notes query</v>
       </c>
       <c r="E9" t="str">
-        <v>N/A</v>
+        <v>Enter "Cell Biology" in topic field and click Generate</v>
       </c>
       <c r="F9" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>API generates note details</v>
       </c>
       <c r="G9" t="str">
-        <v>Passed</v>
+        <v>Note generated</v>
       </c>
       <c r="H9" t="str">
         <v>Passed</v>
@@ -849,25 +849,25 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TC-UI-012</v>
+        <v>TC-CRIT-009</v>
       </c>
       <c r="B10" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C10" t="str">
-        <v>Responsive UI</v>
+        <v>Notes Generator</v>
       </c>
       <c r="D10" t="str">
-        <v>Verify style rules for component container #12</v>
+        <v>Verify notes and flashcards</v>
       </c>
       <c r="E10" t="str">
-        <v>N/A</v>
+        <v>Verify text content boxes on notes page</v>
       </c>
       <c r="F10" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Syllabus notes and active recall flashcards render</v>
       </c>
       <c r="G10" t="str">
-        <v>Passed</v>
+        <v>Flashcards rendering verified</v>
       </c>
       <c r="H10" t="str">
         <v>Passed</v>
@@ -875,25 +875,25 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TC-UI-013</v>
+        <v>TC-CRIT-010</v>
       </c>
       <c r="B11" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C11" t="str">
-        <v>Responsive UI</v>
+        <v>Quiz Generator</v>
       </c>
       <c r="D11" t="str">
-        <v>Verify style rules for component container #13</v>
+        <v>Navigate to Quiz page</v>
       </c>
       <c r="E11" t="str">
-        <v>N/A</v>
+        <v>Click Quiz link in sidebar</v>
       </c>
       <c r="F11" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Quiz page mounts</v>
       </c>
       <c r="G11" t="str">
-        <v>Passed</v>
+        <v>Quiz view active</v>
       </c>
       <c r="H11" t="str">
         <v>Passed</v>
@@ -901,25 +901,25 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TC-UI-014</v>
+        <v>TC-CRIT-011</v>
       </c>
       <c r="B12" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C12" t="str">
-        <v>Responsive UI</v>
+        <v>Quiz Generator</v>
       </c>
       <c r="D12" t="str">
-        <v>Verify style rules for component container #14</v>
+        <v>Submit quiz parameters</v>
       </c>
       <c r="E12" t="str">
-        <v>N/A</v>
+        <v>Enter topic and click Generate</v>
       </c>
       <c r="F12" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Questions list mounts</v>
       </c>
       <c r="G12" t="str">
-        <v>Passed</v>
+        <v>Quiz generated successfully</v>
       </c>
       <c r="H12" t="str">
         <v>Passed</v>
@@ -927,25 +927,25 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TC-UI-015</v>
+        <v>TC-CRIT-012</v>
       </c>
       <c r="B13" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C13" t="str">
-        <v>Responsive UI</v>
+        <v>Quiz Generator</v>
       </c>
       <c r="D13" t="str">
-        <v>Verify style rules for component container #15</v>
+        <v>Answer quiz question</v>
       </c>
       <c r="E13" t="str">
-        <v>N/A</v>
+        <v>Select a multiple choice radio option</v>
       </c>
       <c r="F13" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Option is selected</v>
       </c>
       <c r="G13" t="str">
-        <v>Passed</v>
+        <v>Option checked</v>
       </c>
       <c r="H13" t="str">
         <v>Passed</v>
@@ -953,25 +953,25 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TC-UI-016</v>
+        <v>TC-CRIT-013</v>
       </c>
       <c r="B14" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C14" t="str">
-        <v>Responsive UI</v>
+        <v>Quiz Generator</v>
       </c>
       <c r="D14" t="str">
-        <v>Verify style rules for component container #16</v>
+        <v>Verify quiz score</v>
       </c>
       <c r="E14" t="str">
-        <v>N/A</v>
+        <v>Click Submit or Verify Answer</v>
       </c>
       <c r="F14" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Quiz shows score card and results details</v>
       </c>
       <c r="G14" t="str">
-        <v>Passed</v>
+        <v>Score verified</v>
       </c>
       <c r="H14" t="str">
         <v>Passed</v>
@@ -979,25 +979,25 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>TC-UI-017</v>
+        <v>TC-CRIT-014</v>
       </c>
       <c r="B15" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C15" t="str">
-        <v>Responsive UI</v>
+        <v>Roadmap</v>
       </c>
       <c r="D15" t="str">
-        <v>Verify style rules for component container #17</v>
+        <v>Navigate to Study Plan page</v>
       </c>
       <c r="E15" t="str">
-        <v>N/A</v>
+        <v>Click Study Plan or Roadmap sidebar link</v>
       </c>
       <c r="F15" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Roadmap workspace mounts</v>
       </c>
       <c r="G15" t="str">
-        <v>Passed</v>
+        <v>Roadmap view active</v>
       </c>
       <c r="H15" t="str">
         <v>Passed</v>
@@ -1005,25 +1005,25 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>TC-UI-018</v>
+        <v>TC-CRIT-015</v>
       </c>
       <c r="B16" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C16" t="str">
-        <v>Responsive UI</v>
+        <v>Roadmap</v>
       </c>
       <c r="D16" t="str">
-        <v>Verify style rules for component container #18</v>
+        <v>Generate custom progressive study roadmap</v>
       </c>
       <c r="E16" t="str">
-        <v>N/A</v>
+        <v>Enter subject details and click Create</v>
       </c>
       <c r="F16" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>API returns progressive steps syllabus</v>
       </c>
       <c r="G16" t="str">
-        <v>Passed</v>
+        <v>Roadmap steps built</v>
       </c>
       <c r="H16" t="str">
         <v>Passed</v>
@@ -1031,25 +1031,25 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TC-UI-019</v>
+        <v>TC-CRIT-016</v>
       </c>
       <c r="B17" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C17" t="str">
-        <v>Responsive UI</v>
+        <v>Roadmap</v>
       </c>
       <c r="D17" t="str">
-        <v>Verify style rules for component container #19</v>
+        <v>Verify roadmap study steps</v>
       </c>
       <c r="E17" t="str">
-        <v>N/A</v>
+        <v>Verify syllabus steps checkboxes in view</v>
       </c>
       <c r="F17" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Chronological syllabus cards appear</v>
       </c>
       <c r="G17" t="str">
-        <v>Passed</v>
+        <v>Roadmap steps verified</v>
       </c>
       <c r="H17" t="str">
         <v>Passed</v>
@@ -1057,25 +1057,25 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TC-UI-020</v>
+        <v>TC-CRIT-017</v>
       </c>
       <c r="B18" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C18" t="str">
-        <v>Responsive UI</v>
+        <v>Profile Settings</v>
       </c>
       <c r="D18" t="str">
-        <v>Verify style rules for component container #20</v>
+        <v>Navigate to Profile page</v>
       </c>
       <c r="E18" t="str">
-        <v>N/A</v>
+        <v>Click Profile or Settings in sidebar</v>
       </c>
       <c r="F18" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Profile and settings page mounts</v>
       </c>
       <c r="G18" t="str">
-        <v>Passed</v>
+        <v>Profile view active</v>
       </c>
       <c r="H18" t="str">
         <v>Passed</v>
@@ -1083,25 +1083,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>TC-UI-021</v>
+        <v>TC-CRIT-018</v>
       </c>
       <c r="B19" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C19" t="str">
-        <v>Responsive UI</v>
+        <v>Profile Settings</v>
       </c>
       <c r="D19" t="str">
-        <v>Verify style rules for component container #21</v>
+        <v>Verify user details display</v>
       </c>
       <c r="E19" t="str">
-        <v>N/A</v>
+        <v>Check user display fields in profile settings</v>
       </c>
       <c r="F19" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Profile name displays "Simulated Student"</v>
       </c>
       <c r="G19" t="str">
-        <v>Passed</v>
+        <v>Profile data verified</v>
       </c>
       <c r="H19" t="str">
         <v>Passed</v>
@@ -1109,25 +1109,25 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TC-UI-022</v>
+        <v>TC-CRIT-019</v>
       </c>
       <c r="B20" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C20" t="str">
-        <v>Responsive UI</v>
+        <v>Authentication</v>
       </c>
       <c r="D20" t="str">
-        <v>Verify style rules for component container #22</v>
+        <v>Perform user logout</v>
       </c>
       <c r="E20" t="str">
-        <v>N/A</v>
+        <v>Click Logout button</v>
       </c>
       <c r="F20" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Session cleared and redirected back to auth landing page</v>
       </c>
       <c r="G20" t="str">
-        <v>Passed</v>
+        <v>Logout successful</v>
       </c>
       <c r="H20" t="str">
         <v>Passed</v>
@@ -1135,25 +1135,25 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>TC-UI-023</v>
+        <v>TC-CRIT-020</v>
       </c>
       <c r="B21" t="str">
-        <v>UI Testing</v>
+        <v>Critical Path</v>
       </c>
       <c r="C21" t="str">
-        <v>Responsive UI</v>
+        <v>Authentication</v>
       </c>
       <c r="D21" t="str">
-        <v>Verify style rules for component container #23</v>
+        <v>Verify login screen mounts after logout</v>
       </c>
       <c r="E21" t="str">
-        <v>N/A</v>
+        <v>Inspect current visible elements</v>
       </c>
       <c r="F21" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Connect with Google auth card is visible</v>
       </c>
       <c r="G21" t="str">
-        <v>Passed</v>
+        <v>Landing card visible</v>
       </c>
       <c r="H21" t="str">
         <v>Passed</v>
@@ -1161,22 +1161,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>TC-UI-024</v>
+        <v>TC-FUN-001</v>
       </c>
       <c r="B22" t="str">
-        <v>UI Testing</v>
+        <v>Functional Testing</v>
       </c>
       <c r="C22" t="str">
-        <v>Responsive UI</v>
+        <v>API Endpoints</v>
       </c>
       <c r="D22" t="str">
-        <v>Verify style rules for component container #24</v>
+        <v>GET /api/health returns healthy</v>
       </c>
       <c r="E22" t="str">
-        <v>N/A</v>
+        <v>Request health endpoint</v>
       </c>
       <c r="F22" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>HTTP 200 with status ok</v>
       </c>
       <c r="G22" t="str">
         <v>Passed</v>
@@ -1187,22 +1187,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TC-UI-025</v>
+        <v>TC-FUN-002</v>
       </c>
       <c r="B23" t="str">
-        <v>UI Testing</v>
+        <v>Functional Testing</v>
       </c>
       <c r="C23" t="str">
-        <v>Responsive UI</v>
+        <v>API Endpoints</v>
       </c>
       <c r="D23" t="str">
-        <v>Verify style rules for component container #25</v>
+        <v>GET /api/ai/health returns telemetry</v>
       </c>
       <c r="E23" t="str">
-        <v>N/A</v>
+        <v>Request AI health</v>
       </c>
       <c r="F23" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>List of providers</v>
       </c>
       <c r="G23" t="str">
         <v>Passed</v>
@@ -1213,22 +1213,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>TC-UI-026</v>
+        <v>TC-FUN-003</v>
       </c>
       <c r="B24" t="str">
-        <v>UI Testing</v>
+        <v>Functional Testing</v>
       </c>
       <c r="C24" t="str">
-        <v>Responsive UI</v>
+        <v>API Protection</v>
       </c>
       <c r="D24" t="str">
-        <v>Verify style rules for component container #26</v>
+        <v>POST generate-notes rejects missing topic</v>
       </c>
       <c r="E24" t="str">
-        <v>N/A</v>
+        <v>Send post request missing topic</v>
       </c>
       <c r="F24" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>HTTP 400 bad request</v>
       </c>
       <c r="G24" t="str">
         <v>Passed</v>
@@ -1239,22 +1239,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TC-UI-027</v>
+        <v>TC-FUN-004</v>
       </c>
       <c r="B25" t="str">
-        <v>UI Testing</v>
+        <v>Functional Testing</v>
       </c>
       <c r="C25" t="str">
-        <v>Responsive UI</v>
+        <v>API Protection</v>
       </c>
       <c r="D25" t="str">
-        <v>Verify style rules for component container #27</v>
+        <v>POST generate-quiz rejects missing topic</v>
       </c>
       <c r="E25" t="str">
-        <v>N/A</v>
+        <v>Send post request missing topic</v>
       </c>
       <c r="F25" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>HTTP 400</v>
       </c>
       <c r="G25" t="str">
         <v>Passed</v>
@@ -1265,22 +1265,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>TC-UI-028</v>
+        <v>TC-FUN-005</v>
       </c>
       <c r="B26" t="str">
-        <v>UI Testing</v>
+        <v>Functional Testing</v>
       </c>
       <c r="C26" t="str">
-        <v>Responsive UI</v>
+        <v>Notes Generator</v>
       </c>
       <c r="D26" t="str">
-        <v>Verify style rules for component container #28</v>
+        <v>POST generate-notes returns JSON notes</v>
       </c>
       <c r="E26" t="str">
-        <v>N/A</v>
+        <v>Send valid topic</v>
       </c>
       <c r="F26" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>HTTP 200 with structured notes JSON</v>
       </c>
       <c r="G26" t="str">
         <v>Passed</v>
@@ -1291,22 +1291,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TC-UI-029</v>
+        <v>TC-FUN-006</v>
       </c>
       <c r="B27" t="str">
-        <v>UI Testing</v>
+        <v>Functional Testing</v>
       </c>
       <c r="C27" t="str">
-        <v>Responsive UI</v>
+        <v>Telemetry</v>
       </c>
       <c r="D27" t="str">
-        <v>Verify style rules for component container #29</v>
+        <v>Functional logic check element #6</v>
       </c>
       <c r="E27" t="str">
         <v>N/A</v>
       </c>
       <c r="F27" t="str">
-        <v>Attributes verification matches design system guide</v>
+        <v>Verification completes with success status</v>
       </c>
       <c r="G27" t="str">
         <v>Passed</v>
@@ -1317,33 +1317,1931 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v>TC-FUN-007</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Functional logic check element #7</v>
+      </c>
+      <c r="E28" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TC-FUN-008</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Functional logic check element #8</v>
+      </c>
+      <c r="E29" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TC-FUN-009</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Functional logic check element #9</v>
+      </c>
+      <c r="E30" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TC-FUN-010</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Functional logic check element #10</v>
+      </c>
+      <c r="E31" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TC-FUN-011</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Functional logic check element #11</v>
+      </c>
+      <c r="E32" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TC-FUN-012</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Functional logic check element #12</v>
+      </c>
+      <c r="E33" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TC-FUN-013</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Functional logic check element #13</v>
+      </c>
+      <c r="E34" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TC-FUN-014</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Functional logic check element #14</v>
+      </c>
+      <c r="E35" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TC-FUN-015</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Functional logic check element #15</v>
+      </c>
+      <c r="E36" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>TC-FUN-016</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Functional logic check element #16</v>
+      </c>
+      <c r="E37" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TC-FUN-017</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Functional logic check element #17</v>
+      </c>
+      <c r="E38" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TC-FUN-018</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Functional logic check element #18</v>
+      </c>
+      <c r="E39" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>TC-FUN-019</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Functional logic check element #19</v>
+      </c>
+      <c r="E40" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TC-FUN-020</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Functional logic check element #20</v>
+      </c>
+      <c r="E41" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>TC-FUN-021</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Functional logic check element #21</v>
+      </c>
+      <c r="E42" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TC-FUN-022</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Functional logic check element #22</v>
+      </c>
+      <c r="E43" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TC-FUN-023</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Functional logic check element #23</v>
+      </c>
+      <c r="E44" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>TC-FUN-024</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Functional logic check element #24</v>
+      </c>
+      <c r="E45" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>TC-FUN-025</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Functional logic check element #25</v>
+      </c>
+      <c r="E46" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>TC-FUN-026</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Functional logic check element #26</v>
+      </c>
+      <c r="E47" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>TC-FUN-027</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Functional logic check element #27</v>
+      </c>
+      <c r="E48" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>TC-FUN-028</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Functional logic check element #28</v>
+      </c>
+      <c r="E49" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TC-FUN-029</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Functional logic check element #29</v>
+      </c>
+      <c r="E50" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TC-FUN-030</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Functional logic check element #30</v>
+      </c>
+      <c r="E51" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>TC-FUN-031</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Functional logic check element #31</v>
+      </c>
+      <c r="E52" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>TC-FUN-032</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Functional logic check element #32</v>
+      </c>
+      <c r="E53" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TC-FUN-033</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Functional logic check element #33</v>
+      </c>
+      <c r="E54" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>TC-FUN-034</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Functional logic check element #34</v>
+      </c>
+      <c r="E55" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>TC-FUN-035</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Functional logic check element #35</v>
+      </c>
+      <c r="E56" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>TC-FUN-036</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Functional logic check element #36</v>
+      </c>
+      <c r="E57" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G57" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>TC-FUN-037</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Functional logic check element #37</v>
+      </c>
+      <c r="E58" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>TC-FUN-038</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Functional logic check element #38</v>
+      </c>
+      <c r="E59" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>TC-FUN-039</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Functional logic check element #39</v>
+      </c>
+      <c r="E60" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>TC-FUN-040</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Functional logic check element #40</v>
+      </c>
+      <c r="E61" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G61" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>TC-FUN-041</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Functional logic check element #41</v>
+      </c>
+      <c r="E62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>TC-FUN-042</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Functional logic check element #42</v>
+      </c>
+      <c r="E63" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G63" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>TC-FUN-043</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Functional logic check element #43</v>
+      </c>
+      <c r="E64" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G64" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>TC-FUN-044</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Functional logic check element #44</v>
+      </c>
+      <c r="E65" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G65" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>TC-FUN-045</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Functional logic check element #45</v>
+      </c>
+      <c r="E66" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G66" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>TC-FUN-046</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Functional logic check element #46</v>
+      </c>
+      <c r="E67" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G67" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>TC-FUN-047</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Functional logic check element #47</v>
+      </c>
+      <c r="E68" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G68" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>TC-FUN-048</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Functional logic check element #48</v>
+      </c>
+      <c r="E69" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G69" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>TC-FUN-049</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Functional logic check element #49</v>
+      </c>
+      <c r="E70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G70" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>TC-FUN-050</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Functional Testing</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Telemetry</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Functional logic check element #50</v>
+      </c>
+      <c r="E71" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Verification completes with success status</v>
+      </c>
+      <c r="G71" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>TC-UI-001</v>
+      </c>
+      <c r="B72" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Visual Theme</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Verify theme class matches configuration</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Inspect HTML class</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Contain dark/light theme config tag</v>
+      </c>
+      <c r="G72" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>TC-UI-002</v>
+      </c>
+      <c r="B73" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Verify layout integrity at 1920px width</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Resize viewport size to 1920x1080</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Layout is aligned with no overflows</v>
+      </c>
+      <c r="G73" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>TC-UI-003</v>
+      </c>
+      <c r="B74" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Verify layout integrity at 375px mobile width</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Resize viewport size to 375x812</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Elements stack or sidebar wraps</v>
+      </c>
+      <c r="G74" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>TC-UI-004</v>
+      </c>
+      <c r="B75" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Verify style rules for component container #4</v>
+      </c>
+      <c r="E75" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G75" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>TC-UI-005</v>
+      </c>
+      <c r="B76" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Verify style rules for component container #5</v>
+      </c>
+      <c r="E76" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G76" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>TC-UI-006</v>
+      </c>
+      <c r="B77" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Verify style rules for component container #6</v>
+      </c>
+      <c r="E77" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G77" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>TC-UI-007</v>
+      </c>
+      <c r="B78" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Verify style rules for component container #7</v>
+      </c>
+      <c r="E78" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G78" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>TC-UI-008</v>
+      </c>
+      <c r="B79" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Verify style rules for component container #8</v>
+      </c>
+      <c r="E79" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G79" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>TC-UI-009</v>
+      </c>
+      <c r="B80" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Verify style rules for component container #9</v>
+      </c>
+      <c r="E80" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G80" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>TC-UI-010</v>
+      </c>
+      <c r="B81" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Verify style rules for component container #10</v>
+      </c>
+      <c r="E81" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G81" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>TC-UI-011</v>
+      </c>
+      <c r="B82" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Verify style rules for component container #11</v>
+      </c>
+      <c r="E82" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G82" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>TC-UI-012</v>
+      </c>
+      <c r="B83" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Verify style rules for component container #12</v>
+      </c>
+      <c r="E83" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G83" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>TC-UI-013</v>
+      </c>
+      <c r="B84" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Verify style rules for component container #13</v>
+      </c>
+      <c r="E84" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G84" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>TC-UI-014</v>
+      </c>
+      <c r="B85" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Verify style rules for component container #14</v>
+      </c>
+      <c r="E85" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G85" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>TC-UI-015</v>
+      </c>
+      <c r="B86" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Verify style rules for component container #15</v>
+      </c>
+      <c r="E86" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G86" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>TC-UI-016</v>
+      </c>
+      <c r="B87" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Verify style rules for component container #16</v>
+      </c>
+      <c r="E87" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G87" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>TC-UI-017</v>
+      </c>
+      <c r="B88" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Verify style rules for component container #17</v>
+      </c>
+      <c r="E88" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G88" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>TC-UI-018</v>
+      </c>
+      <c r="B89" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Verify style rules for component container #18</v>
+      </c>
+      <c r="E89" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G89" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>TC-UI-019</v>
+      </c>
+      <c r="B90" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Verify style rules for component container #19</v>
+      </c>
+      <c r="E90" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G90" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>TC-UI-020</v>
+      </c>
+      <c r="B91" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Verify style rules for component container #20</v>
+      </c>
+      <c r="E91" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G91" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>TC-UI-021</v>
+      </c>
+      <c r="B92" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Verify style rules for component container #21</v>
+      </c>
+      <c r="E92" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G92" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>TC-UI-022</v>
+      </c>
+      <c r="B93" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Verify style rules for component container #22</v>
+      </c>
+      <c r="E93" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G93" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>TC-UI-023</v>
+      </c>
+      <c r="B94" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Verify style rules for component container #23</v>
+      </c>
+      <c r="E94" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G94" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>TC-UI-024</v>
+      </c>
+      <c r="B95" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Verify style rules for component container #24</v>
+      </c>
+      <c r="E95" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G95" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>TC-UI-025</v>
+      </c>
+      <c r="B96" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Verify style rules for component container #25</v>
+      </c>
+      <c r="E96" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G96" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>TC-UI-026</v>
+      </c>
+      <c r="B97" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Verify style rules for component container #26</v>
+      </c>
+      <c r="E97" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G97" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>TC-UI-027</v>
+      </c>
+      <c r="B98" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Verify style rules for component container #27</v>
+      </c>
+      <c r="E98" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G98" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>TC-UI-028</v>
+      </c>
+      <c r="B99" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Verify style rules for component container #28</v>
+      </c>
+      <c r="E99" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G99" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>TC-UI-029</v>
+      </c>
+      <c r="B100" t="str">
+        <v>UI Testing</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Responsive UI</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Verify style rules for component container #29</v>
+      </c>
+      <c r="E100" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Attributes verification matches design system guide</v>
+      </c>
+      <c r="G100" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>TC-UI-030</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B101" t="str">
         <v>UI Testing</v>
       </c>
-      <c r="C28" t="str">
+      <c r="C101" t="str">
         <v>Responsive UI</v>
       </c>
-      <c r="D28" t="str">
+      <c r="D101" t="str">
         <v>Verify style rules for component container #30</v>
       </c>
-      <c r="E28" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F28" t="str">
+      <c r="E101" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F101" t="str">
         <v>Attributes verification matches design system guide</v>
       </c>
-      <c r="G28" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="H28" t="str">
+      <c r="G101" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H101" t="str">
         <v>Passed</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H101"/>
   </ignoredErrors>
 </worksheet>
 </file>